--- a/raw-data/Salads_Pricing_Comparison.xlsx
+++ b/raw-data/Salads_Pricing_Comparison.xlsx
@@ -25,7 +25,7 @@
     <author>Unknown Author</author>
   </authors>
   <commentList>
-    <comment ref="C7" authorId="0">
+    <comment ref="E7" authorId="0">
       <text>
         <r>
           <rPr>
@@ -37,7 +37,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C8" authorId="0">
+    <comment ref="E8" authorId="0">
       <text>
         <r>
           <rPr>
@@ -49,7 +49,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C9" authorId="0">
+    <comment ref="E9" authorId="0">
       <text>
         <r>
           <rPr>
@@ -61,7 +61,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C12" authorId="0">
+    <comment ref="E12" authorId="0">
       <text>
         <r>
           <rPr>
@@ -73,7 +73,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C23" authorId="0">
+    <comment ref="E23" authorId="0">
       <text>
         <r>
           <rPr>
@@ -85,7 +85,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C28" authorId="0">
+    <comment ref="E28" authorId="0">
       <text>
         <r>
           <rPr>
@@ -97,7 +97,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C33" authorId="0">
+    <comment ref="E33" authorId="0">
       <text>
         <r>
           <rPr>
@@ -109,7 +109,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C34" authorId="0">
+    <comment ref="E34" authorId="0">
       <text>
         <r>
           <rPr>
@@ -121,7 +121,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C43" authorId="0">
+    <comment ref="E43" authorId="0">
       <text>
         <r>
           <rPr>
@@ -133,7 +133,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D7" authorId="0">
+    <comment ref="G7" authorId="0">
       <text>
         <r>
           <rPr>
@@ -145,7 +145,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D8" authorId="0">
+    <comment ref="G8" authorId="0">
       <text>
         <r>
           <rPr>
@@ -157,7 +157,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D9" authorId="0">
+    <comment ref="G9" authorId="0">
       <text>
         <r>
           <rPr>
@@ -169,7 +169,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D18" authorId="0">
+    <comment ref="G18" authorId="0">
       <text>
         <r>
           <rPr>
@@ -181,7 +181,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D20" authorId="0">
+    <comment ref="G20" authorId="0">
       <text>
         <r>
           <rPr>
@@ -193,7 +193,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D21" authorId="0">
+    <comment ref="G21" authorId="0">
       <text>
         <r>
           <rPr>
@@ -205,7 +205,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D31" authorId="0">
+    <comment ref="G31" authorId="0">
       <text>
         <r>
           <rPr>
@@ -217,7 +217,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D32" authorId="0">
+    <comment ref="G32" authorId="0">
       <text>
         <r>
           <rPr>
@@ -229,7 +229,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D35" authorId="0">
+    <comment ref="G35" authorId="0">
       <text>
         <r>
           <rPr>
@@ -241,7 +241,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D37" authorId="0">
+    <comment ref="G37" authorId="0">
       <text>
         <r>
           <rPr>
@@ -253,7 +253,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D39" authorId="0">
+    <comment ref="G39" authorId="0">
       <text>
         <r>
           <rPr>
@@ -265,7 +265,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D40" authorId="0">
+    <comment ref="G40" authorId="0">
       <text>
         <r>
           <rPr>
@@ -277,7 +277,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D42" authorId="0">
+    <comment ref="G42" authorId="0">
       <text>
         <r>
           <rPr>
@@ -289,7 +289,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D45" authorId="0">
+    <comment ref="G45" authorId="0">
       <text>
         <r>
           <rPr>
@@ -301,7 +301,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D46" authorId="0">
+    <comment ref="G46" authorId="0">
       <text>
         <r>
           <rPr>
@@ -313,7 +313,20 @@
         </r>
       </text>
     </comment>
-    <comment ref="E8" authorId="0">
+    <comment ref="I4" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Casper &amp; Gambini 'Asian Bowl' - $9.50 x 89,600 = 851,200 LBP. Source: user-provided pricing data, July 2026.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I8" authorId="0">
       <text>
         <r>
           <rPr>
@@ -325,7 +338,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E11" authorId="0">
+    <comment ref="I11" authorId="0">
       <text>
         <r>
           <rPr>
@@ -337,19 +350,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E16" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Casper &amp; Gambini 'Asian Bowl' - $9.50 x 89,600 = 851,200 LBP. Source: user-provided pricing data, July 2026.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E17" authorId="0">
+    <comment ref="I17" authorId="0">
       <text>
         <r>
           <rPr>
@@ -361,7 +362,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E25" authorId="0">
+    <comment ref="I25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -373,7 +374,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E27" authorId="0">
+    <comment ref="I27" authorId="0">
       <text>
         <r>
           <rPr>
@@ -385,7 +386,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E30" authorId="0">
+    <comment ref="I30" authorId="0">
       <text>
         <r>
           <rPr>
@@ -397,7 +398,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E36" authorId="0">
+    <comment ref="I36" authorId="0">
       <text>
         <r>
           <rPr>
@@ -409,7 +410,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E38" authorId="0">
+    <comment ref="I38" authorId="0">
       <text>
         <r>
           <rPr>
@@ -421,7 +422,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E44" authorId="0">
+    <comment ref="I44" authorId="0">
       <text>
         <r>
           <rPr>
@@ -433,7 +434,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F5" authorId="0">
+    <comment ref="M5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -445,7 +446,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F7" authorId="0">
+    <comment ref="M7" authorId="0">
       <text>
         <r>
           <rPr>
@@ -457,7 +458,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F9" authorId="0">
+    <comment ref="M9" authorId="0">
       <text>
         <r>
           <rPr>
@@ -469,7 +470,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F19" authorId="0">
+    <comment ref="M19" authorId="0">
       <text>
         <r>
           <rPr>
@@ -481,7 +482,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F22" authorId="0">
+    <comment ref="M22" authorId="0">
       <text>
         <r>
           <rPr>
@@ -493,7 +494,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F24" authorId="0">
+    <comment ref="M24" authorId="0">
       <text>
         <r>
           <rPr>
@@ -505,7 +506,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F26" authorId="0">
+    <comment ref="M26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -517,7 +518,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F29" authorId="0">
+    <comment ref="M29" authorId="0">
       <text>
         <r>
           <rPr>
@@ -529,7 +530,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F41" authorId="0">
+    <comment ref="M41" authorId="0">
       <text>
         <r>
           <rPr>
@@ -546,7 +547,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="76">
   <si>
     <t xml:space="preserve">Products Competitors</t>
   </si>
@@ -563,6 +564,9 @@
     <t xml:space="preserve">Casper &amp; Gambini</t>
   </si>
   <si>
+    <t xml:space="preserve">Pain D’or</t>
+  </si>
+  <si>
     <t xml:space="preserve">The Koozspace</t>
   </si>
   <si>
@@ -572,48 +576,96 @@
     <t xml:space="preserve">Difference</t>
   </si>
   <si>
+    <t xml:space="preserve">PORTION SIZE (g)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRICED PORTION (G)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALSO AVAILABLE (G)</t>
+  </si>
+  <si>
     <t xml:space="preserve">SALADS</t>
   </si>
   <si>
+    <t xml:space="preserve">-</t>
+  </si>
+  <si>
     <t xml:space="preserve">SALAD BAR 1 VISIT</t>
   </si>
   <si>
-    <t xml:space="preserve">-</t>
-  </si>
-  <si>
     <t xml:space="preserve">ASIAN SALAD (GRAB&amp;GO)</t>
   </si>
   <si>
+    <t xml:space="preserve">380 g.</t>
+  </si>
+  <si>
     <t xml:space="preserve">GREEK SALAD (GRAB&amp;GO)</t>
   </si>
   <si>
+    <t xml:space="preserve">500-600g.</t>
+  </si>
+  <si>
     <t xml:space="preserve">QUINOA SALAD (GRAB&amp;GO)</t>
   </si>
   <si>
+    <t xml:space="preserve">320 g.</t>
+  </si>
+  <si>
     <t xml:space="preserve">TUNA PASTA SALAD (GRAB&amp;GO)</t>
   </si>
   <si>
+    <t xml:space="preserve">440 g.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">550 g.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200 g.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">paind’or</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500-600</t>
+  </si>
+  <si>
     <t xml:space="preserve">CAESAR SALAD (GRAB&amp;GO)</t>
   </si>
   <si>
+    <t xml:space="preserve">235 g.</t>
+  </si>
+  <si>
     <t xml:space="preserve">CHICKEN CAESAR SALAD (GRAB&amp;GO)</t>
   </si>
   <si>
+    <t xml:space="preserve">360 g.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">345 g.</t>
+  </si>
+  <si>
     <t xml:space="preserve">CHICKEN VERDE SALAD (GRAB&amp;GO)</t>
   </si>
   <si>
     <t xml:space="preserve">MEXICAN FIESTA SALAD (GRAB&amp;GO)</t>
   </si>
   <si>
+    <t xml:space="preserve">450 g.</t>
+  </si>
+  <si>
     <t xml:space="preserve">PASTA PESTO SALAD (GRAB&amp;GO)</t>
   </si>
   <si>
+    <t xml:space="preserve">445 g.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">580 g.</t>
+  </si>
+  <si>
     <t xml:space="preserve">COMPETITOR ITEMS NOT ON STORIES MENU (gap analysis - Stories left blank)</t>
   </si>
   <si>
-    <t xml:space="preserve">ASIAN BOWL</t>
-  </si>
-  <si>
     <t xml:space="preserve">ASIAN SESAME CHICKEN</t>
   </si>
   <si>
@@ -635,6 +687,9 @@
     <t xml:space="preserve">CRAB CRUNCH</t>
   </si>
   <si>
+    <t xml:space="preserve">352 g.</t>
+  </si>
+  <si>
     <t xml:space="preserve">CRAB SALAD</t>
   </si>
   <si>
@@ -650,6 +705,9 @@
     <t xml:space="preserve">GREEK ORZO</t>
   </si>
   <si>
+    <t xml:space="preserve">408 g.</t>
+  </si>
+  <si>
     <t xml:space="preserve">GREEN SALAD</t>
   </si>
   <si>
@@ -665,9 +723,15 @@
     <t xml:space="preserve">KALE QUINOA CHICKEN</t>
   </si>
   <si>
+    <t xml:space="preserve">300 g.</t>
+  </si>
+  <si>
     <t xml:space="preserve">KALE QUINOA HALLOUMI</t>
   </si>
   <si>
+    <t xml:space="preserve">276 g.</t>
+  </si>
+  <si>
     <t xml:space="preserve">LEBANESE ORIENTAL</t>
   </si>
   <si>
@@ -695,6 +759,9 @@
     <t xml:space="preserve">THE PROTEIN CLUB</t>
   </si>
   <si>
+    <t xml:space="preserve">430 g.</t>
+  </si>
+  <si>
     <t xml:space="preserve">TUNA POTATO</t>
   </si>
   <si>
@@ -702,6 +769,12 @@
   </si>
   <si>
     <t xml:space="preserve">ZOOZA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">grilled veggie salad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">light slim line salad</t>
   </si>
 </sst>
 </file>
@@ -712,7 +785,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -752,6 +825,12 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -802,49 +881,41 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1099,1295 +1170,1785 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H52"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:R52"/>
+  <sheetFormatPr defaultColWidth="10.16015625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="33.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="6.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="6.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="15.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="6.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="13.76"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="10.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="17.81"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="10.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="9.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="1" width="14.74"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="10.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="11.19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="16.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="19.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="19.15"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="19" style="2" width="10.16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3"/>
+      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="3"/>
+      <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="F1" s="3"/>
+      <c r="G1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="H1" s="3"/>
+      <c r="I1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="J1" s="3"/>
+      <c r="K1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="L1" s="3"/>
+      <c r="M1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="O1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="R1" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="A2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
+      <c r="P2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="5" t="n">
+      <c r="A3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="6"/>
+      <c r="C3" s="7" t="n">
         <v>1200000</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" s="5" t="n">
-        <f aca="false">AVERAGE(B3:F3)</f>
+      <c r="D3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="N3" s="7" t="n">
+        <f aca="false">AVERAGE(C3:M3)</f>
         <v>1200000</v>
       </c>
-      <c r="H3" s="5" t="n">
-        <f aca="false">IF(ISNUMBER(B3),B3-G3,"-")</f>
+      <c r="O3" s="7" t="n">
+        <f aca="false">IF(ISNUMBER(C3),C3-N3,"-")</f>
         <v>0</v>
       </c>
+      <c r="P3" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q3" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="R3" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="5" t="n">
+      <c r="A4" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="7" t="n">
         <v>750000</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <f aca="false">AVERAGE(B4:F4)</f>
+      <c r="D4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="6"/>
+      <c r="I4" s="7" t="n">
+        <v>851200</v>
+      </c>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="N4" s="7" t="n">
+        <f aca="false">AVERAGE(C4:M4)</f>
+        <v>800600</v>
+      </c>
+      <c r="O4" s="7" t="n">
+        <f aca="false">IF(ISNUMBER(C4),C4-N4,"-")</f>
+        <v>-50600</v>
+      </c>
+      <c r="P4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q4" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="R4" s="1" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="6"/>
+      <c r="C5" s="7" t="n">
         <v>750000</v>
       </c>
-      <c r="H4" s="5" t="n">
-        <f aca="false">IF(ISNUMBER(B4),B4-G4,"-")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="5" t="n">
+      <c r="D5" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K5" s="6" t="n">
+        <v>895000</v>
+      </c>
+      <c r="L5" s="6"/>
+      <c r="M5" s="7" t="n">
+        <v>896000</v>
+      </c>
+      <c r="N5" s="7" t="n">
+        <f aca="false">AVERAGE(C5:M5)</f>
+        <v>847000</v>
+      </c>
+      <c r="O5" s="7" t="n">
+        <f aca="false">IF(ISNUMBER(C5),C5-N5,"-")</f>
+        <v>-97000</v>
+      </c>
+      <c r="P5" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q5" s="1" t="n">
+        <v>400</v>
+      </c>
+      <c r="R5" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>800000</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K6" s="6" t="n">
+        <v>1074000</v>
+      </c>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="N6" s="7" t="n">
+        <f aca="false">AVERAGE(C6:M6)</f>
+        <v>937000</v>
+      </c>
+      <c r="O6" s="7" t="n">
+        <f aca="false">IF(ISNUMBER(C6),C6-N6,"-")</f>
+        <v>-137000</v>
+      </c>
+      <c r="P6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q6" s="1" t="n">
+        <v>400</v>
+      </c>
+      <c r="R6" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>850000</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>716800</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>806400</v>
+      </c>
+      <c r="H7" s="7"/>
+      <c r="I7" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K7" s="6" t="n">
+        <v>1074000</v>
+      </c>
+      <c r="L7" s="6"/>
+      <c r="M7" s="7" t="n">
+        <v>1075200</v>
+      </c>
+      <c r="N7" s="7" t="n">
+        <f aca="false">AVERAGE(C7:M7)</f>
+        <v>904480</v>
+      </c>
+      <c r="O7" s="7" t="n">
+        <f aca="false">IF(ISNUMBER(C7),C7-N7,"-")</f>
+        <v>-54480</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="6"/>
+      <c r="C8" s="7" t="n">
         <v>750000</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="5" t="n">
-        <v>896000</v>
-      </c>
-      <c r="G5" s="5" t="n">
-        <f aca="false">AVERAGE(B5:F5)</f>
-        <v>823000</v>
-      </c>
-      <c r="H5" s="5" t="n">
-        <f aca="false">IF(ISNUMBER(B5),B5-G5,"-")</f>
-        <v>-73000</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="5" t="n">
-        <v>800000</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <f aca="false">AVERAGE(B6:F6)</f>
-        <v>800000</v>
-      </c>
-      <c r="H6" s="5" t="n">
-        <f aca="false">IF(ISNUMBER(B6),B6-G6,"-")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="5" t="n">
-        <v>850000</v>
-      </c>
-      <c r="C7" s="5" t="n">
+      <c r="D8" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>537600</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>358400</v>
+      </c>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7" t="n">
         <v>716800</v>
       </c>
-      <c r="D7" s="5" t="n">
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="N8" s="7" t="n">
+        <f aca="false">AVERAGE(C8:M8)</f>
+        <v>590700</v>
+      </c>
+      <c r="O8" s="7" t="n">
+        <f aca="false">IF(ISNUMBER(C8),C8-N8,"-")</f>
+        <v>159300</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="8" t="n">
+        <v>900000</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" s="7" t="n">
         <v>806400</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>1075200</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <f aca="false">AVERAGE(B7:F7)</f>
-        <v>862100</v>
-      </c>
-      <c r="H7" s="5" t="n">
-        <f aca="false">IF(ISNUMBER(B7),B7-G7,"-")</f>
-        <v>-12100</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="5" t="n">
-        <v>750000</v>
-      </c>
-      <c r="C8" s="5" t="n">
-        <v>537600</v>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>358400</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>716800</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" s="5" t="n">
-        <f aca="false">AVERAGE(B8:F8)</f>
-        <v>590700</v>
-      </c>
-      <c r="H8" s="5" t="n">
-        <f aca="false">IF(ISNUMBER(B8),B8-G8,"-")</f>
-        <v>159300</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="6" t="n">
-        <v>900000</v>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>806400</v>
-      </c>
-      <c r="D9" s="5" t="n">
+      <c r="F9" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" s="7" t="n">
         <v>627200</v>
       </c>
-      <c r="E9" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" s="5" t="n">
+      <c r="H9" s="7"/>
+      <c r="I9" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K9" s="6" t="n">
+        <v>1074000</v>
+      </c>
+      <c r="L9" s="6"/>
+      <c r="M9" s="7" t="n">
         <v>985600</v>
       </c>
-      <c r="G9" s="5" t="n">
-        <f aca="false">AVERAGE(B9:F9)</f>
-        <v>829800</v>
-      </c>
-      <c r="H9" s="5" t="n">
-        <f aca="false">IF(ISNUMBER(B9),B9-G9,"-")</f>
-        <v>70200</v>
+      <c r="N9" s="7" t="n">
+        <f aca="false">AVERAGE(C9:M9)</f>
+        <v>878640</v>
+      </c>
+      <c r="O9" s="7" t="n">
+        <f aca="false">IF(ISNUMBER(C9),C9-N9,"-")</f>
+        <v>21360</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="8" t="n">
         <v>850000</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10" s="5" t="n">
-        <f aca="false">AVERAGE(B10:F10)</f>
+      <c r="D10" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="2"/>
+      <c r="G10" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="N10" s="7" t="n">
+        <f aca="false">AVERAGE(C10:M10)</f>
         <v>850000</v>
       </c>
-      <c r="H10" s="5" t="n">
-        <f aca="false">IF(ISNUMBER(B10),B10-G10,"-")</f>
+      <c r="O10" s="7" t="n">
+        <f aca="false">IF(ISNUMBER(C10),C10-N10,"-")</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="8" t="n">
         <v>900000</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" s="5" t="n">
+      <c r="D11" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11" s="6"/>
+      <c r="I11" s="7" t="n">
         <v>806400</v>
       </c>
-      <c r="F11" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11" s="5" t="n">
-        <f aca="false">AVERAGE(B11:F11)</f>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="N11" s="7" t="n">
+        <f aca="false">AVERAGE(C11:M11)</f>
         <v>853200</v>
       </c>
-      <c r="H11" s="5" t="n">
-        <f aca="false">IF(ISNUMBER(B11),B11-G11,"-")</f>
+      <c r="O11" s="7" t="n">
+        <f aca="false">IF(ISNUMBER(C11),C11-N11,"-")</f>
         <v>46800</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="8" t="n">
         <v>900000</v>
       </c>
-      <c r="C12" s="5" t="n">
+      <c r="D12" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" s="7" t="n">
         <v>896000</v>
       </c>
-      <c r="D12" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12" s="5" t="n">
-        <f aca="false">AVERAGE(B12:F12)</f>
+      <c r="F12" s="7"/>
+      <c r="G12" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="6"/>
+      <c r="M12" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="N12" s="7" t="n">
+        <f aca="false">AVERAGE(C12:M12)</f>
         <v>898000</v>
       </c>
-      <c r="H12" s="5" t="n">
-        <f aca="false">IF(ISNUMBER(B12),B12-G12,"-")</f>
+      <c r="O12" s="7" t="n">
+        <f aca="false">IF(ISNUMBER(C12),C12-N12,"-")</f>
         <v>2000</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="7"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="6"/>
     </row>
     <row r="14" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
+      <c r="A14" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="5"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="5"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6"/>
+      <c r="M15" s="6"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="6"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E16" s="5" t="n">
-        <v>851200</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G16" s="5" t="n">
-        <f aca="false">AVERAGE(B16:F16)</f>
-        <v>851200</v>
-      </c>
-      <c r="H16" s="5" t="str">
-        <f aca="false">IF(ISNUMBER(B16),B16-G16,"-")</f>
-        <v>-</v>
-      </c>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="7"/>
+      <c r="M16" s="6"/>
+      <c r="N16" s="7"/>
+      <c r="O16" s="7"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E17" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17" s="6"/>
+      <c r="I17" s="7" t="n">
         <v>940800</v>
       </c>
-      <c r="F17" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G17" s="5" t="n">
-        <f aca="false">AVERAGE(B17:F17)</f>
+      <c r="J17" s="7"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="7"/>
+      <c r="M17" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="N17" s="7" t="n">
+        <f aca="false">AVERAGE(C17:M17)</f>
         <v>940800</v>
       </c>
-      <c r="H17" s="5" t="str">
-        <f aca="false">IF(ISNUMBER(B17),B17-G17,"-")</f>
+      <c r="O17" s="7" t="str">
+        <f aca="false">IF(ISNUMBER(C17),C17-N17,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D18" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G18" s="7" t="n">
         <v>716800</v>
       </c>
-      <c r="E18" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G18" s="5" t="n">
-        <f aca="false">AVERAGE(B18:F18)</f>
+      <c r="H18" s="7"/>
+      <c r="I18" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J18" s="6"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6"/>
+      <c r="M18" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="N18" s="7" t="n">
+        <f aca="false">AVERAGE(C18:M18)</f>
         <v>716800</v>
       </c>
-      <c r="H18" s="5" t="str">
-        <f aca="false">IF(ISNUMBER(B18),B18-G18,"-")</f>
+      <c r="O18" s="7" t="str">
+        <f aca="false">IF(ISNUMBER(C18),C18-N18,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="D19" s="4"/>
+      <c r="E19" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19" s="6"/>
+      <c r="I19" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J19" s="6"/>
+      <c r="K19" s="6"/>
+      <c r="L19" s="6"/>
+      <c r="M19" s="7" t="n">
         <v>1075200</v>
       </c>
-      <c r="G19" s="5" t="n">
-        <f aca="false">AVERAGE(B19:F19)</f>
+      <c r="N19" s="7" t="n">
+        <f aca="false">AVERAGE(C19:M19)</f>
         <v>1075200</v>
       </c>
-      <c r="H19" s="5" t="str">
-        <f aca="false">IF(ISNUMBER(B19),B19-G19,"-")</f>
+      <c r="O19" s="7" t="str">
+        <f aca="false">IF(ISNUMBER(C19),C19-N19,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D20" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="D20" s="4"/>
+      <c r="E20" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G20" s="7" t="n">
         <v>806400</v>
       </c>
-      <c r="E20" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G20" s="5" t="n">
-        <f aca="false">AVERAGE(B20:F20)</f>
+      <c r="H20" s="7"/>
+      <c r="I20" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J20" s="6"/>
+      <c r="K20" s="6"/>
+      <c r="L20" s="6"/>
+      <c r="M20" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="N20" s="7" t="n">
+        <f aca="false">AVERAGE(C20:M20)</f>
         <v>806400</v>
       </c>
-      <c r="H20" s="5" t="str">
-        <f aca="false">IF(ISNUMBER(B20),B20-G20,"-")</f>
+      <c r="O20" s="7" t="str">
+        <f aca="false">IF(ISNUMBER(C20),C20-N20,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D21" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G21" s="8" t="n">
         <v>716800</v>
       </c>
-      <c r="E21" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G21" s="9" t="n">
-        <f aca="false">AVERAGE(B21:F21)</f>
+      <c r="H21" s="8"/>
+      <c r="I21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N21" s="8" t="n">
+        <f aca="false">AVERAGE(C21:M21)</f>
         <v>716800</v>
       </c>
-      <c r="H21" s="9" t="str">
-        <f aca="false">IF(ISNUMBER(B21),B21-G21,"-")</f>
+      <c r="O21" s="8" t="str">
+        <f aca="false">IF(ISNUMBER(C21),C21-N21,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>10</v>
-      </c>
+      <c r="A22" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" s="3"/>
       <c r="C22" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="M22" s="8" t="n">
         <v>1164800</v>
       </c>
-      <c r="G22" s="9" t="n">
-        <f aca="false">AVERAGE(B22:F22)</f>
+      <c r="N22" s="8" t="n">
+        <f aca="false">AVERAGE(C22:M22)</f>
         <v>1164800</v>
       </c>
-      <c r="H22" s="9" t="str">
-        <f aca="false">IF(ISNUMBER(B22),B22-G22,"-")</f>
+      <c r="O22" s="8" t="str">
+        <f aca="false">IF(ISNUMBER(C22),C22-N22,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E23" s="8" t="n">
         <v>627200</v>
       </c>
-      <c r="D23" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G23" s="10" t="n">
-        <f aca="false">AVERAGE(B23:F23)</f>
+      <c r="F23" s="8"/>
+      <c r="G23" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N23" s="8" t="n">
+        <f aca="false">AVERAGE(C23:M23)</f>
         <v>627200</v>
       </c>
-      <c r="H23" s="10" t="str">
-        <f aca="false">IF(ISNUMBER(B23),B23-G23,"-")</f>
+      <c r="O23" s="8" t="str">
+        <f aca="false">IF(ISNUMBER(C23),C23-N23,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24" s="5" t="n">
+      <c r="A24" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H24" s="6"/>
+      <c r="I24" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K24" s="6" t="n">
+        <v>1074000</v>
+      </c>
+      <c r="L24" s="6"/>
+      <c r="M24" s="7" t="n">
         <v>806400</v>
       </c>
-      <c r="G24" s="5" t="n">
-        <f aca="false">AVERAGE(B24:F24)</f>
-        <v>806400</v>
-      </c>
-      <c r="H24" s="5" t="str">
-        <f aca="false">IF(ISNUMBER(B24),B24-G24,"-")</f>
+      <c r="N24" s="7" t="n">
+        <f aca="false">AVERAGE(C24:M24)</f>
+        <v>940200</v>
+      </c>
+      <c r="O24" s="7" t="str">
+        <f aca="false">IF(ISNUMBER(C24),C24-N24,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E25" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I25" s="8" t="n">
         <v>761600</v>
       </c>
-      <c r="F25" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G25" s="10" t="n">
-        <f aca="false">AVERAGE(B25:F25)</f>
+      <c r="J25" s="8"/>
+      <c r="K25" s="8"/>
+      <c r="L25" s="8"/>
+      <c r="M25" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N25" s="8" t="n">
+        <f aca="false">AVERAGE(C25:M25)</f>
         <v>761600</v>
       </c>
-      <c r="H25" s="10" t="str">
-        <f aca="false">IF(ISNUMBER(B25),B25-G25,"-")</f>
+      <c r="O25" s="8" t="str">
+        <f aca="false">IF(ISNUMBER(C25),C25-N25,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F26" s="5" t="n">
+      <c r="A26" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26" s="6"/>
+      <c r="C26" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H26" s="6"/>
+      <c r="I26" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J26" s="6"/>
+      <c r="K26" s="6"/>
+      <c r="L26" s="6"/>
+      <c r="M26" s="7" t="n">
         <v>1344000</v>
       </c>
-      <c r="G26" s="5" t="n">
-        <f aca="false">AVERAGE(B26:F26)</f>
+      <c r="N26" s="7" t="n">
+        <f aca="false">AVERAGE(C26:M26)</f>
         <v>1344000</v>
       </c>
-      <c r="H26" s="5" t="str">
-        <f aca="false">IF(ISNUMBER(B26),B26-G26,"-")</f>
+      <c r="O26" s="7" t="str">
+        <f aca="false">IF(ISNUMBER(C26),C26-N26,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E27" s="5" t="n">
+      <c r="A27" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B27" s="6"/>
+      <c r="C27" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F27" s="6"/>
+      <c r="G27" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H27" s="6"/>
+      <c r="I27" s="7" t="n">
         <v>851200</v>
       </c>
-      <c r="F27" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G27" s="5" t="n">
-        <f aca="false">AVERAGE(B27:F27)</f>
+      <c r="J27" s="7"/>
+      <c r="K27" s="7"/>
+      <c r="L27" s="7"/>
+      <c r="M27" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="N27" s="7" t="n">
+        <f aca="false">AVERAGE(C27:M27)</f>
         <v>851200</v>
       </c>
-      <c r="H27" s="5" t="str">
-        <f aca="false">IF(ISNUMBER(B27),B27-G27,"-")</f>
+      <c r="O27" s="7" t="str">
+        <f aca="false">IF(ISNUMBER(C27),C27-N27,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="5" t="n">
+      <c r="A28" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B28" s="6"/>
+      <c r="C28" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="E28" s="7" t="n">
         <v>672000</v>
       </c>
-      <c r="D28" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G28" s="5" t="n">
-        <f aca="false">AVERAGE(B28:F28)</f>
+      <c r="F28" s="7"/>
+      <c r="G28" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H28" s="6"/>
+      <c r="I28" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J28" s="6"/>
+      <c r="K28" s="6"/>
+      <c r="L28" s="6"/>
+      <c r="M28" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="N28" s="7" t="n">
+        <f aca="false">AVERAGE(C28:M28)</f>
         <v>672000</v>
       </c>
-      <c r="H28" s="5" t="str">
-        <f aca="false">IF(ISNUMBER(B28),B28-G28,"-")</f>
+      <c r="O28" s="7" t="str">
+        <f aca="false">IF(ISNUMBER(C28),C28-N28,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F29" s="5" t="n">
+      <c r="A29" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B29" s="6"/>
+      <c r="C29" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D29" s="6"/>
+      <c r="E29" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F29" s="6"/>
+      <c r="G29" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H29" s="6"/>
+      <c r="I29" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J29" s="6"/>
+      <c r="K29" s="6"/>
+      <c r="L29" s="6"/>
+      <c r="M29" s="7" t="n">
         <v>627200</v>
       </c>
-      <c r="G29" s="5" t="n">
-        <f aca="false">AVERAGE(B29:F29)</f>
+      <c r="N29" s="7" t="n">
+        <f aca="false">AVERAGE(C29:M29)</f>
         <v>627200</v>
       </c>
-      <c r="H29" s="5" t="str">
-        <f aca="false">IF(ISNUMBER(B29),B29-G29,"-")</f>
+      <c r="O29" s="7" t="str">
+        <f aca="false">IF(ISNUMBER(C29),C29-N29,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E30" s="5" t="n">
+      <c r="A30" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B30" s="6"/>
+      <c r="C30" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F30" s="6"/>
+      <c r="G30" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H30" s="6"/>
+      <c r="I30" s="7" t="n">
         <v>1075200</v>
       </c>
-      <c r="F30" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G30" s="5" t="n">
-        <f aca="false">AVERAGE(B30:F30)</f>
+      <c r="J30" s="7"/>
+      <c r="K30" s="7"/>
+      <c r="L30" s="7"/>
+      <c r="M30" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="N30" s="7" t="n">
+        <f aca="false">AVERAGE(C30:M30)</f>
         <v>1075200</v>
       </c>
-      <c r="H30" s="5" t="str">
-        <f aca="false">IF(ISNUMBER(B30),B30-G30,"-")</f>
+      <c r="O30" s="7" t="str">
+        <f aca="false">IF(ISNUMBER(C30),C30-N30,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D31" s="5" t="n">
+      <c r="A31" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B31" s="6"/>
+      <c r="C31" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G31" s="7" t="n">
         <v>716800</v>
       </c>
-      <c r="E31" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G31" s="5" t="n">
-        <f aca="false">AVERAGE(B31:F31)</f>
+      <c r="H31" s="7"/>
+      <c r="I31" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J31" s="6"/>
+      <c r="K31" s="6"/>
+      <c r="L31" s="6"/>
+      <c r="M31" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="N31" s="7" t="n">
+        <f aca="false">AVERAGE(C31:M31)</f>
         <v>716800</v>
       </c>
-      <c r="H31" s="5" t="str">
-        <f aca="false">IF(ISNUMBER(B31),B31-G31,"-")</f>
+      <c r="O31" s="7" t="str">
+        <f aca="false">IF(ISNUMBER(C31),C31-N31,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D32" s="5" t="n">
+      <c r="A32" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G32" s="7" t="n">
         <v>716800</v>
       </c>
-      <c r="E32" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G32" s="5" t="n">
-        <f aca="false">AVERAGE(B32:F32)</f>
+      <c r="H32" s="7"/>
+      <c r="I32" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J32" s="6"/>
+      <c r="K32" s="6"/>
+      <c r="L32" s="6"/>
+      <c r="M32" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="N32" s="7" t="n">
+        <f aca="false">AVERAGE(C32:M32)</f>
         <v>716800</v>
       </c>
-      <c r="H32" s="5" t="str">
-        <f aca="false">IF(ISNUMBER(B32),B32-G32,"-")</f>
+      <c r="O32" s="7" t="str">
+        <f aca="false">IF(ISNUMBER(C32),C32-N32,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="5" t="n">
+      <c r="A33" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B33" s="6"/>
+      <c r="C33" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E33" s="7" t="n">
         <v>896000</v>
       </c>
-      <c r="D33" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G33" s="5" t="n">
-        <f aca="false">AVERAGE(B33:F33)</f>
+      <c r="F33" s="7"/>
+      <c r="G33" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H33" s="6"/>
+      <c r="I33" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J33" s="6"/>
+      <c r="K33" s="6"/>
+      <c r="L33" s="6"/>
+      <c r="M33" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="N33" s="7" t="n">
+        <f aca="false">AVERAGE(C33:M33)</f>
         <v>896000</v>
       </c>
-      <c r="H33" s="5" t="str">
-        <f aca="false">IF(ISNUMBER(B33),B33-G33,"-")</f>
+      <c r="O33" s="7" t="str">
+        <f aca="false">IF(ISNUMBER(C33),C33-N33,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="5" t="n">
+      <c r="A34" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B34" s="6"/>
+      <c r="C34" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E34" s="7" t="n">
         <v>716800</v>
       </c>
-      <c r="D34" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G34" s="5" t="n">
-        <f aca="false">AVERAGE(B34:F34)</f>
+      <c r="F34" s="7"/>
+      <c r="G34" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H34" s="6"/>
+      <c r="I34" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J34" s="6"/>
+      <c r="K34" s="6"/>
+      <c r="L34" s="6"/>
+      <c r="M34" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="N34" s="7" t="n">
+        <f aca="false">AVERAGE(C34:M34)</f>
         <v>716800</v>
       </c>
-      <c r="H34" s="5" t="str">
-        <f aca="false">IF(ISNUMBER(B34),B34-G34,"-")</f>
+      <c r="O34" s="7" t="str">
+        <f aca="false">IF(ISNUMBER(C34),C34-N34,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D35" s="5" t="n">
+      <c r="A35" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B35" s="6"/>
+      <c r="C35" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D35" s="6"/>
+      <c r="E35" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G35" s="7" t="n">
         <v>448000</v>
       </c>
-      <c r="E35" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G35" s="5" t="n">
-        <f aca="false">AVERAGE(B35:F35)</f>
+      <c r="H35" s="7"/>
+      <c r="I35" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J35" s="6"/>
+      <c r="K35" s="6"/>
+      <c r="L35" s="6"/>
+      <c r="M35" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="N35" s="7" t="n">
+        <f aca="false">AVERAGE(C35:M35)</f>
         <v>448000</v>
       </c>
-      <c r="H35" s="5" t="str">
-        <f aca="false">IF(ISNUMBER(B35),B35-G35,"-")</f>
+      <c r="O35" s="7" t="str">
+        <f aca="false">IF(ISNUMBER(C35),C35-N35,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E36" s="5" t="n">
+      <c r="A36" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B36" s="6"/>
+      <c r="C36" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H36" s="6"/>
+      <c r="I36" s="7" t="n">
         <v>896000</v>
       </c>
-      <c r="F36" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G36" s="5" t="n">
-        <f aca="false">AVERAGE(B36:F36)</f>
+      <c r="J36" s="7"/>
+      <c r="K36" s="7"/>
+      <c r="L36" s="7"/>
+      <c r="M36" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="N36" s="7" t="n">
+        <f aca="false">AVERAGE(C36:M36)</f>
         <v>896000</v>
       </c>
-      <c r="H36" s="5" t="str">
-        <f aca="false">IF(ISNUMBER(B36),B36-G36,"-")</f>
+      <c r="O36" s="7" t="str">
+        <f aca="false">IF(ISNUMBER(C36),C36-N36,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D37" s="5" t="n">
+      <c r="A37" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B37" s="6"/>
+      <c r="C37" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G37" s="7" t="n">
         <v>806400</v>
       </c>
-      <c r="E37" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G37" s="5" t="n">
-        <f aca="false">AVERAGE(B37:F37)</f>
+      <c r="H37" s="7"/>
+      <c r="I37" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J37" s="6"/>
+      <c r="K37" s="6"/>
+      <c r="L37" s="6"/>
+      <c r="M37" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="N37" s="7" t="n">
+        <f aca="false">AVERAGE(C37:M37)</f>
         <v>806400</v>
       </c>
-      <c r="H37" s="5" t="str">
-        <f aca="false">IF(ISNUMBER(B37),B37-G37,"-")</f>
+      <c r="O37" s="7" t="str">
+        <f aca="false">IF(ISNUMBER(C37),C37-N37,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E38" s="5" t="n">
+      <c r="A38" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B38" s="6"/>
+      <c r="C38" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F38" s="6"/>
+      <c r="G38" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H38" s="6"/>
+      <c r="I38" s="7" t="n">
         <v>896000</v>
       </c>
-      <c r="F38" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G38" s="5" t="n">
-        <f aca="false">AVERAGE(B38:F38)</f>
+      <c r="J38" s="7"/>
+      <c r="K38" s="7"/>
+      <c r="L38" s="7"/>
+      <c r="M38" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="N38" s="7" t="n">
+        <f aca="false">AVERAGE(C38:M38)</f>
         <v>896000</v>
       </c>
-      <c r="H38" s="5" t="str">
-        <f aca="false">IF(ISNUMBER(B38),B38-G38,"-")</f>
+      <c r="O38" s="7" t="str">
+        <f aca="false">IF(ISNUMBER(C38),C38-N38,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D39" s="5" t="n">
+      <c r="A39" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B39" s="6"/>
+      <c r="C39" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G39" s="7" t="n">
         <v>716800</v>
       </c>
-      <c r="E39" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F39" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G39" s="5" t="n">
-        <f aca="false">AVERAGE(B39:F39)</f>
+      <c r="H39" s="7"/>
+      <c r="I39" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J39" s="6"/>
+      <c r="K39" s="6"/>
+      <c r="L39" s="6"/>
+      <c r="M39" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="N39" s="7" t="n">
+        <f aca="false">AVERAGE(C39:M39)</f>
         <v>716800</v>
       </c>
-      <c r="H39" s="5" t="str">
-        <f aca="false">IF(ISNUMBER(B39),B39-G39,"-")</f>
+      <c r="O39" s="7" t="str">
+        <f aca="false">IF(ISNUMBER(C39),C39-N39,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D40" s="5" t="n">
+      <c r="A40" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G40" s="7" t="n">
         <v>448000</v>
       </c>
-      <c r="E40" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F40" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G40" s="5" t="n">
-        <f aca="false">AVERAGE(B40:F40)</f>
+      <c r="H40" s="7"/>
+      <c r="I40" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J40" s="6"/>
+      <c r="K40" s="6"/>
+      <c r="L40" s="6"/>
+      <c r="M40" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="N40" s="7" t="n">
+        <f aca="false">AVERAGE(C40:M40)</f>
         <v>448000</v>
       </c>
-      <c r="H40" s="5" t="str">
-        <f aca="false">IF(ISNUMBER(B40),B40-G40,"-")</f>
+      <c r="O40" s="7" t="str">
+        <f aca="false">IF(ISNUMBER(C40),C40-N40,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E41" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F41" s="5" t="n">
+      <c r="A41" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B41" s="6"/>
+      <c r="C41" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F41" s="6"/>
+      <c r="G41" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H41" s="6"/>
+      <c r="I41" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J41" s="6"/>
+      <c r="K41" s="0"/>
+      <c r="L41" s="0"/>
+      <c r="M41" s="7" t="n">
         <v>716800</v>
       </c>
-      <c r="G41" s="5" t="n">
-        <f aca="false">AVERAGE(B41:F41)</f>
+      <c r="N41" s="7" t="n">
+        <f aca="false">AVERAGE(C41:M41)</f>
         <v>716800</v>
       </c>
-      <c r="H41" s="5" t="str">
-        <f aca="false">IF(ISNUMBER(B41),B41-G41,"-")</f>
+      <c r="O41" s="7" t="str">
+        <f aca="false">IF(ISNUMBER(C41),C41-N41,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D42" s="5" t="n">
+      <c r="A42" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B42" s="6"/>
+      <c r="C42" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F42" s="6"/>
+      <c r="G42" s="7" t="n">
         <v>716800</v>
       </c>
-      <c r="E42" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F42" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G42" s="5" t="n">
-        <f aca="false">AVERAGE(B42:F42)</f>
+      <c r="H42" s="7"/>
+      <c r="I42" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J42" s="6"/>
+      <c r="K42" s="6"/>
+      <c r="L42" s="6"/>
+      <c r="M42" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="N42" s="7" t="n">
+        <f aca="false">AVERAGE(C42:M42)</f>
         <v>716800</v>
       </c>
-      <c r="H42" s="5" t="str">
-        <f aca="false">IF(ISNUMBER(B42),B42-G42,"-")</f>
+      <c r="O42" s="7" t="str">
+        <f aca="false">IF(ISNUMBER(C42),C42-N42,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="5" t="n">
+      <c r="A43" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="E43" s="7" t="n">
         <v>985600</v>
       </c>
-      <c r="D43" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E43" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F43" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G43" s="5" t="n">
-        <f aca="false">AVERAGE(B43:F43)</f>
+      <c r="F43" s="7"/>
+      <c r="G43" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H43" s="6"/>
+      <c r="I43" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J43" s="6"/>
+      <c r="K43" s="6"/>
+      <c r="L43" s="6"/>
+      <c r="M43" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="N43" s="7" t="n">
+        <f aca="false">AVERAGE(C43:M43)</f>
         <v>985600</v>
       </c>
-      <c r="H43" s="5" t="str">
-        <f aca="false">IF(ISNUMBER(B43),B43-G43,"-")</f>
+      <c r="O43" s="7" t="str">
+        <f aca="false">IF(ISNUMBER(C43),C43-N43,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E44" s="5" t="n">
+      <c r="A44" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B44" s="6"/>
+      <c r="C44" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D44" s="6"/>
+      <c r="E44" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F44" s="6"/>
+      <c r="G44" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H44" s="6"/>
+      <c r="I44" s="7" t="n">
         <v>851200</v>
       </c>
-      <c r="F44" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G44" s="5" t="n">
-        <f aca="false">AVERAGE(B44:F44)</f>
+      <c r="J44" s="7"/>
+      <c r="K44" s="7"/>
+      <c r="L44" s="7"/>
+      <c r="M44" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="N44" s="7" t="n">
+        <f aca="false">AVERAGE(C44:M44)</f>
         <v>851200</v>
       </c>
-      <c r="H44" s="5" t="str">
-        <f aca="false">IF(ISNUMBER(B44),B44-G44,"-")</f>
+      <c r="O44" s="7" t="str">
+        <f aca="false">IF(ISNUMBER(C44),C44-N44,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D45" s="5" t="n">
+      <c r="A45" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B45" s="6"/>
+      <c r="C45" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D45" s="6"/>
+      <c r="E45" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G45" s="7" t="n">
         <v>448000</v>
       </c>
-      <c r="E45" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F45" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G45" s="5" t="n">
-        <f aca="false">AVERAGE(B45:F45)</f>
+      <c r="H45" s="7"/>
+      <c r="I45" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J45" s="6"/>
+      <c r="K45" s="6"/>
+      <c r="L45" s="6"/>
+      <c r="M45" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="N45" s="7" t="n">
+        <f aca="false">AVERAGE(C45:M45)</f>
         <v>448000</v>
       </c>
-      <c r="H45" s="5" t="str">
-        <f aca="false">IF(ISNUMBER(B45),B45-G45,"-")</f>
+      <c r="O45" s="7" t="str">
+        <f aca="false">IF(ISNUMBER(C45),C45-N45,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D46" s="5" t="n">
+      <c r="A46" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B46" s="6"/>
+      <c r="C46" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D46" s="6"/>
+      <c r="E46" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G46" s="7" t="n">
         <v>806400</v>
       </c>
-      <c r="E46" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F46" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G46" s="5" t="n">
-        <f aca="false">AVERAGE(B46:F46)</f>
+      <c r="H46" s="7"/>
+      <c r="I46" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J46" s="6"/>
+      <c r="K46" s="6"/>
+      <c r="L46" s="6"/>
+      <c r="M46" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="N46" s="7" t="n">
+        <f aca="false">AVERAGE(C46:M46)</f>
         <v>806400</v>
       </c>
-      <c r="H46" s="5" t="str">
-        <f aca="false">IF(ISNUMBER(B46),B46-G46,"-")</f>
+      <c r="O46" s="7" t="str">
+        <f aca="false">IF(ISNUMBER(C46),C46-N46,"-")</f>
         <v>-</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="4"/>
-      <c r="B47" s="4"/>
-      <c r="C47" s="4"/>
-      <c r="D47" s="4"/>
-      <c r="E47" s="4"/>
-      <c r="F47" s="4"/>
-      <c r="G47" s="4"/>
-      <c r="H47" s="4"/>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="4"/>
-      <c r="B48" s="4"/>
-      <c r="C48" s="4"/>
-      <c r="D48" s="4"/>
-      <c r="E48" s="4"/>
-      <c r="F48" s="4"/>
-      <c r="G48" s="4"/>
-      <c r="H48" s="4"/>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="4"/>
-      <c r="B49" s="4"/>
-      <c r="C49" s="4"/>
-      <c r="D49" s="4"/>
-      <c r="E49" s="4"/>
-      <c r="F49" s="4"/>
-      <c r="G49" s="4"/>
-      <c r="H49" s="4"/>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="4"/>
-      <c r="B50" s="4"/>
-      <c r="C50" s="4"/>
-      <c r="D50" s="4"/>
-      <c r="E50" s="4"/>
-      <c r="F50" s="4"/>
-      <c r="G50" s="4"/>
-      <c r="H50" s="4"/>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="4"/>
-      <c r="B51" s="4"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="4"/>
-      <c r="E51" s="4"/>
-      <c r="F51" s="4"/>
-      <c r="G51" s="4"/>
-      <c r="H51" s="4"/>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="4"/>
-      <c r="B52" s="4"/>
-      <c r="C52" s="4"/>
-      <c r="D52" s="4"/>
-      <c r="E52" s="4"/>
-      <c r="F52" s="4"/>
-      <c r="G52" s="4"/>
-      <c r="H52" s="4"/>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B47" s="6"/>
+      <c r="C47" s="6"/>
+      <c r="D47" s="6"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="6"/>
+      <c r="G47" s="6"/>
+      <c r="H47" s="6"/>
+      <c r="I47" s="6"/>
+      <c r="J47" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K47" s="6" t="n">
+        <v>1074000</v>
+      </c>
+      <c r="L47" s="6"/>
+      <c r="M47" s="6"/>
+      <c r="N47" s="6"/>
+      <c r="O47" s="6"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="B48" s="6"/>
+      <c r="C48" s="6"/>
+      <c r="D48" s="6"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="6"/>
+      <c r="G48" s="6"/>
+      <c r="H48" s="6"/>
+      <c r="I48" s="6"/>
+      <c r="J48" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K48" s="6" t="n">
+        <v>1074000</v>
+      </c>
+      <c r="L48" s="6"/>
+      <c r="M48" s="6"/>
+      <c r="N48" s="6"/>
+      <c r="O48" s="6"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="6"/>
+      <c r="B49" s="6"/>
+      <c r="C49" s="6"/>
+      <c r="D49" s="6"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="6"/>
+      <c r="G49" s="6"/>
+      <c r="H49" s="6"/>
+      <c r="I49" s="6"/>
+      <c r="J49" s="6"/>
+      <c r="K49" s="6"/>
+      <c r="L49" s="6"/>
+      <c r="M49" s="6"/>
+      <c r="N49" s="6"/>
+      <c r="O49" s="6"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="6"/>
+      <c r="B50" s="6"/>
+      <c r="C50" s="6"/>
+      <c r="D50" s="6"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="6"/>
+      <c r="G50" s="6"/>
+      <c r="H50" s="6"/>
+      <c r="I50" s="6"/>
+      <c r="J50" s="6"/>
+      <c r="K50" s="6"/>
+      <c r="L50" s="6"/>
+      <c r="M50" s="6"/>
+      <c r="N50" s="6"/>
+      <c r="O50" s="6"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="6"/>
+      <c r="B51" s="6"/>
+      <c r="C51" s="6"/>
+      <c r="D51" s="6"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="6"/>
+      <c r="G51" s="6"/>
+      <c r="H51" s="6"/>
+      <c r="I51" s="6"/>
+      <c r="J51" s="6"/>
+      <c r="K51" s="6"/>
+      <c r="L51" s="6"/>
+      <c r="M51" s="6"/>
+      <c r="N51" s="6"/>
+      <c r="O51" s="6"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="6"/>
+      <c r="B52" s="6"/>
+      <c r="C52" s="6"/>
+      <c r="D52" s="6"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="6"/>
+      <c r="G52" s="6"/>
+      <c r="H52" s="6"/>
+      <c r="I52" s="6"/>
+      <c r="J52" s="6"/>
+      <c r="K52" s="6"/>
+      <c r="L52" s="6"/>
+      <c r="M52" s="6"/>
+      <c r="N52" s="6"/>
+      <c r="O52" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A2:O2"/>
+    <mergeCell ref="A14:O14"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
